--- a/AAII_Financials/Quarterly/BHF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BHF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>BHF</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1611000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1515000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1907000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1808000</v>
       </c>
-      <c r="G8" s="3">
-        <v>860000</v>
-      </c>
       <c r="H8" s="3">
+        <v>863000</v>
+      </c>
+      <c r="I8" s="3">
         <v>2373000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2789000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2010000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1440000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>56000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1758000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1169000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>264000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1284000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>1121000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3866000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2013000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2016000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2512000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1676000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>938000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>131000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>309000</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3">
         <v>8985000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>306000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3187000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2370000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>691000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4026000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1422000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1702000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1815000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1880000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1972000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2026000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>965000</v>
       </c>
-      <c r="AO8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP8" s="3">
+      <c r="AP8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ8" s="3">
         <v>1770000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1279000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1288000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1385000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>462000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1397000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1358000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1379000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>728000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1301000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1621000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1387000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1171000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1298000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1265000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>155000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>159000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>158000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>157000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>127000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>-82000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>91000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>-156000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>244000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>-92000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>770000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>181000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>170000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>22000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>469000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>30000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>246000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>305000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>231000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>123000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>21000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>-148000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>416000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>332000</v>
+      </c>
+      <c r="E10" s="3">
         <v>227000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>522000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1346000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-537000</v>
-      </c>
       <c r="H10" s="3">
+        <v>-534000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1015000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1410000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1282000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>139000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1565000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>371000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1034000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3">
         <v>962000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3708000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1856000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1889000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2594000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1668000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>847000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>287000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>65000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="3">
         <v>8215000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>297000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3006000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2200000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>669000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3557000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1392000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1456000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1510000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1649000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1849000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2005000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1113000</v>
       </c>
-      <c r="AO10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP10" s="3">
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ10" s="3">
         <v>1780000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1543,8 +1562,8 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>4</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>4</v>
@@ -1555,26 +1574,29 @@
       <c r="AJ14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>1000</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>167000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>165000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>358000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2475000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1501000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1193000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>740000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2706000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>333000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1792000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1375000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>650000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2535000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>542000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>462000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1899000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-206000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>571000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1651000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-28000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1926000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1981000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1615000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1665000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1392000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4105000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1555000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2686000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1631000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2334000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1853000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1597000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2194000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1750000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1986000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1891000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2065000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2062000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1668000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1510000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2188000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1978000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-960000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>406000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>615000</v>
       </c>
-      <c r="G18" s="3">
-        <v>120000</v>
-      </c>
       <c r="H18" s="3">
+        <v>123000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-333000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2456000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>218000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>65000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-594000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-777000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>627000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-198000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-615000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>550000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2215000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2041000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>90000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>531000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>61000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-727000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1261000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3796000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3">
         <v>6299000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1325000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>853000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>517000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-906000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1832000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-328000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-284000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-76000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-185000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-90000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>358000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-545000</v>
       </c>
-      <c r="AO18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP18" s="3">
+      <c r="AP18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ18" s="3">
         <v>-208000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2033,35 +2066,35 @@
         <v>-11000</v>
       </c>
       <c r="E20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F20" s="3">
         <v>38000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-11000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-13000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-105000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-13000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-23000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
@@ -2071,8 +2104,8 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -2098,11 +2131,11 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
@@ -2140,59 +2173,62 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
-      <c r="AO20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP20" s="3">
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1264000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-949000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>368000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>622000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>131000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-320000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2561000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>226000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>53000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-581000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-754000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>627000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-198000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-615000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2268,55 +2304,58 @@
       <c r="AP21" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E22" s="3">
         <v>37000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>218000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>37000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>34000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1727000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>38000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>420000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>37000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>38000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>38000</v>
       </c>
       <c r="S22" s="3">
         <v>38000</v>
@@ -2325,317 +2364,326 @@
         <v>38000</v>
       </c>
       <c r="U22" s="3">
-        <v>41000</v>
+        <v>38000</v>
       </c>
       <c r="V22" s="3">
         <v>41000</v>
       </c>
       <c r="W22" s="3">
+        <v>41000</v>
+      </c>
+      <c r="X22" s="3">
         <v>40000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>41000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>45000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>47000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>45000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>47000</v>
       </c>
       <c r="AC22" s="3">
         <v>47000</v>
       </c>
       <c r="AD22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>49000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>48000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>47000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>45000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>40000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>33000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>37000</v>
       </c>
       <c r="AK22" s="3">
         <v>37000</v>
       </c>
       <c r="AL22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="AM22" s="3">
         <v>34000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>37000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>45000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>42000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>44000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-986000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>150000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>585000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>93000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-354000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>834000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>188000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-614000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1174000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>590000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-237000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-653000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>40000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>512000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2177000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2003000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>49000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>490000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-768000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1306000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3843000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2522000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6252000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1372000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>804000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>469000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-953000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1787000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-368000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-317000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-113000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-222000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-124000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>321000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-590000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-2777000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-252000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-222000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>104000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-88000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>162000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-20000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-123000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-258000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>109000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-62000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-156000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-97000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>97000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>432000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>416000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-15000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>105000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-10000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-185000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-275000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-850000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-531000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1293000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-303000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>119000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>85000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-218000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>345000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-99000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-79000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-165000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>819000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>75000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-241000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-1012000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>981000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-764000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>138000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>481000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>85000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-266000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>672000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>178000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-491000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-916000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>481000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-175000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-497000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>137000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>415000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1745000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1587000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>64000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>385000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>31000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-583000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1031000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2993000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1991000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4959000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1069000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>685000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>384000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-735000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1442000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-269000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-238000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-65000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-57000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-943000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>246000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-349000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-1765000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-158000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>956000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-792000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>453000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>60000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-294000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>646000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>150000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-519000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-942000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>453000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-525000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>110000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>388000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1719000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1558000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>361000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1045000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3012000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1998000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4950000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>676000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>377000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-737000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1442000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-271000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-239000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-67000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-57000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-943000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>246000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-349000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-1765000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-158000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>4</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>4</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL29" s="3">
         <v>725000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>4</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3497,35 +3566,35 @@
         <v>11000</v>
       </c>
       <c r="E32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-38000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7000</v>
       </c>
-      <c r="G32" s="3">
-        <v>11000</v>
-      </c>
       <c r="H32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I32" s="3">
         <v>13000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>105000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>13000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>23000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3535,8 +3604,8 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -3562,11 +3631,11 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
@@ -3604,136 +3673,142 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
-      <c r="AO32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP32" s="3">
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>981000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-766000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>137000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>479000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>85000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-268000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>671000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>176000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-493000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-917000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>479000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-175000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-499000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>110000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>388000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1719000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1558000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>42000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>361000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1045000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3012000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1998000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4950000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>676000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>377000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-737000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1442000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-271000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-239000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-67000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>668000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-943000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>246000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-349000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-1765000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-158000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>981000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-766000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>137000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>479000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>85000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-268000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>671000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>176000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-493000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-917000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>479000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-175000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-499000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>110000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>388000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1719000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1558000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>42000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>361000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1045000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3012000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1998000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4950000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>676000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>377000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-737000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1442000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-271000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-239000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-67000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>668000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-943000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>246000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-349000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-1765000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-158000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7105000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4907000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5387000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6606000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5540000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4667000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5045000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5630000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4441000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3823000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3851000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3839000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3737000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3685000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4115000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4793000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5071000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4101000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4474000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4108000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4882000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4025000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4108000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6189000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7325000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8930000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2877000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4289000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3981000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3864000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4145000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2144000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2135000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1888000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1857000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1698000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4443000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5812000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5228000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1766000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2058000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2000000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1306000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1690000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2194000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2155000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1812000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1609000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1606000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1414000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1450000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1403000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1793000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E43" s="3">
         <v>20993000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>60000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21414000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21432000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21417000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>67000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20978000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20082000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20291000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19149000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19307000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19051000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18548000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>17877000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16642000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16290000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16094000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16298000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>16127000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>16129000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>16158000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>16087000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>14895000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14678000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14543000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>14082000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>13978000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>13807000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>13469000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>13385000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>13409000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>13327000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>13298000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>644000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>442000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>591000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2019000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>599000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13846000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9541000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7742000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9129000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9118000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5202000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5125000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5533000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4294000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4905000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4652000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3212000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3766000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3220000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22941000</v>
+      </c>
+      <c r="E46" s="3">
         <v>37499000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15189000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38455000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37780000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33480000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12392000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>33953000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>30426000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30625000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9996000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27650000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28213000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27749000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,130 +5024,136 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>86332000</v>
+      </c>
+      <c r="E47" s="3">
         <v>86829000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>87621000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>87252000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>86515000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>86348000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>85744000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>88928000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>86158000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>86037000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>86390000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>80801000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>82926000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>82844000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>104338000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>103915000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>105770000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>108833000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>113954000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>111361000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>107019000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>99952000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>106721000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>105767000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>104819000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>102236000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>93419000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>96190000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>89475000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>85787000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>82731000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>81763000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>81293000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>81440000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>82645000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>83024000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>82930000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>80298000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>81195000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>99681000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5089,131 +5196,134 @@
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>4775000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4607000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4683000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4587000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4271000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3959000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3546000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3219000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2810000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2562000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2354000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2505000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2380000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>458000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>462000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>453000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>451000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>444000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>449000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>441000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>433000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>407000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>302000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>242000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>215000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>210000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4487000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4520000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4567000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4603000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4636000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4672000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4710000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4745000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4791000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4829000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4872000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4919000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4968000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5027000</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -5244,53 +5354,56 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD49" s="3">
         <v>502000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH49" s="3">
         <v>568000</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL49" s="3">
         <v>1144000</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AO49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP49" s="3">
         <v>1206000</v>
       </c>
-      <c r="AP49" s="3" t="s">
+      <c r="AQ49" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,62 +5649,65 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>107764000</v>
+      </c>
+      <c r="E52" s="3">
         <v>82035000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>108716000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>88477000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>87541000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>83826000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>108446000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>91419000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>89817000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>91765000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>109303000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>83984000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>89592000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>88565000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1736000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1619000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>471000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
@@ -5604,8 +5723,8 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -5631,32 +5750,35 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>4</v>
+      <c r="AI52" s="3">
+        <v>0</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL52" s="3">
         <v>3000</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AM52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AN52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AO52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP52" s="3">
         <v>2000</v>
       </c>
-      <c r="AP52" s="3" t="s">
+      <c r="AQ52" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>247180000</v>
+      </c>
+      <c r="E54" s="3">
         <v>236803000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>241800000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>244679000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>242645000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>234681000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>238537000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>245156000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>237438000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>239688000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>236340000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>223516000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>231545000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>230002000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>224847000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>221641000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>228211000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>245052000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>259840000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>254691000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>253856000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>241937000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>247869000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>239681000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>235367000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>223953000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>227259000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>225876000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>221212000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>216430000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>206294000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>216946000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>216212000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>218997000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>224192000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>223279000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>224328000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>223188000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>221930000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>240929000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,8 +6116,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6031,8 +6161,8 @@
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8646000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6770000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6790000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6318000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6027000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5973000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6626000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5350000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5962000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6391000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5879000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7419000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6391000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6396000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21003000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17640000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15558000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18540000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18183000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14334000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14053000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15097000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13780000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13659000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11065000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8552000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9494000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7745000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>198647000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>204841000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>208226000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>224034000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>234910000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>229097000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>228215000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>217590000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>219714000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>210668000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>197157000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>186527000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>195818000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>192790000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>191210000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>187904000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>180365000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>192279000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>191591000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>194290000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>197923000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>195793000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>194966000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>196709000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>194162000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>212070000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29649000</v>
+      </c>
+      <c r="E60" s="3">
         <v>24410000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22348000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24858000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>24210000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20307000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20679000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20447000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19742000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20050000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16944000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15971000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15885000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14141000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,8 +6614,11 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6484,10 +6626,10 @@
         <v>3154000</v>
       </c>
       <c r="E61" s="3">
+        <v>3154000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3152000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>3155000</v>
       </c>
       <c r="G61" s="3">
         <v>3155000</v>
@@ -6508,25 +6650,25 @@
         <v>3155000</v>
       </c>
       <c r="M61" s="3">
+        <v>3155000</v>
+      </c>
+      <c r="N61" s="3">
         <v>3156000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3157000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3156000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3157000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>3156000</v>
       </c>
       <c r="R61" s="3">
         <v>3156000</v>
       </c>
       <c r="S61" s="3">
-        <v>3157000</v>
+        <v>3156000</v>
       </c>
       <c r="T61" s="3">
         <v>3157000</v>
@@ -6535,25 +6677,25 @@
         <v>3157000</v>
       </c>
       <c r="V61" s="3">
-        <v>3436000</v>
+        <v>3157000</v>
       </c>
       <c r="W61" s="3">
         <v>3436000</v>
       </c>
       <c r="X61" s="3">
+        <v>3436000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>3435000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3436000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>3979000</v>
       </c>
       <c r="AA61" s="3">
         <v>3979000</v>
       </c>
       <c r="AB61" s="3">
-        <v>4365000</v>
+        <v>3979000</v>
       </c>
       <c r="AC61" s="3">
         <v>4365000</v>
@@ -6565,85 +6707,88 @@
         <v>4365000</v>
       </c>
       <c r="AF61" s="3">
+        <v>4365000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>4364000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3963000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3966000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3607000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3609000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3612000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3615000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3016000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1907000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1910000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>814000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>207762000</v>
+      </c>
+      <c r="E62" s="3">
         <v>203611000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>209396000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>210238000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>209542000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>205915000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>209604000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>215964000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>210335000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>212223000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>211149000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>200254000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>207532000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>206885000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6651,76 +6796,79 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>215000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1062000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1120000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1109000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>812000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1620000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1816000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2567000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2482000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1355000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1749000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1364000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1005000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>873000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>576000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>684000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>752000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>816000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2116000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2337000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2445000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2159000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>9875000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>240565000</v>
+      </c>
+      <c r="E66" s="3">
         <v>231175000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>234967000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>238251000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>236907000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>229377000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>233513000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>239566000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>233232000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>235428000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>231332000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>219382000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>226573000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>224183000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>219314000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>215827000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>218020000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>232238000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>243698000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>238660000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>237741000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>226920000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>229846000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>221415000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>214458000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>203579000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>211087000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>208181000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>204936000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>201431000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>191876000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>204062000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>202777000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>205389000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>209677000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>209513000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>207913000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>208072000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>207068000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>222759000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,119 +7909,122 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-471000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1452000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-686000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-823000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1302000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1387000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1119000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1790000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1966000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2000000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1507000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-590000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1069000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-894000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-395000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>304000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>981000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-642000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-705000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1088000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1119000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-534000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>511000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3523000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5521000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>585000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1662000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>986000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>609000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1346000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-96000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>175000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>374000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>406000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>39000</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7861,8 +8034,11 @@
       <c r="AP72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6550000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5563000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6768000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6363000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5673000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5239000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4959000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5525000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4141000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4195000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4943000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4069000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4907000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5754000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5533000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5814000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10191000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12814000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16142000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16031000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16115000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15017000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18023000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18266000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20909000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20374000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16172000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17695000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>16276000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14999000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14418000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12884000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13435000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13608000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>14515000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13766000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>16415000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>15116000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14862000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>18170000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>981000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-766000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>137000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>479000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>85000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-268000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>671000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>176000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-493000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-917000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>479000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-175000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-499000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>110000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>388000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1719000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1558000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>42000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>361000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-610000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1045000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3012000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1998000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4950000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>676000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>377000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-737000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1442000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-271000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-239000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-67000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>668000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-943000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>246000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-349000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-1765000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-158000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8808,8 +9006,8 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-431000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-221000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>117000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>146000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-118000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>334000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-530000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>152000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>339000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-128000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-212000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-957000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>181000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-163000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>102000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>575000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>173000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-104000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>373000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>48000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>371000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>96000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>506000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>513000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>433000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>376000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1566000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>479000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>726000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>291000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1366000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>705000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>965000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>360000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1131000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>471000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-485000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1296000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1372000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>112000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>563000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-357000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-130000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1082000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-625000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-552000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-985000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-334000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1325000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-680000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2577000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2500000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2519000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2573000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5253000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4212000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1659000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2059000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-641000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1484000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1642000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2767000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1660000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1272000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1069000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1446000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1120000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-903000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1361000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-193000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2339000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-22000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>9748000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-561000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2726000</v>
+      </c>
+      <c r="E100" s="3">
         <v>226000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>80000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-423000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>762000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1087000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-110000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1295000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1366000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1127000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>412000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>748000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>514000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1395000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>151000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3261000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3311000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2345000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2837000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3904000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4896000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>221000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-795000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>875000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1335000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>7441000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-276000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2562000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1344000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>615000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1504000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>976000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>641000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>643000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>154000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3257000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>5000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>246000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-8476000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>394000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2198000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-480000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1219000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1066000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>873000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-378000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-585000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1189000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>618000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-28000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>102000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-430000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-678000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-278000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>970000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-373000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>366000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-774000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>857000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-83000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2081000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1136000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1605000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6053000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1412000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>308000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>117000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-281000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2001000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>247000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>31000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>159000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2745000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1369000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>584000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>2403000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>304000</v>
       </c>
     </row>
